--- a/public/samples/en/sample2.xlsx
+++ b/public/samples/en/sample2.xlsx
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Jack White</v>
+        <v>Leo Taylor</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
@@ -780,13 +780,13 @@
         <v>F</v>
       </c>
       <c r="D17" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F17" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="18">
@@ -794,19 +794,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Leo Johnson</v>
+        <v>Henry Anderson</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2" t="str">
         <v/>
       </c>
       <c r="F18" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="19">
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Lily Baker</v>
+        <v>Lily Hill</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="20">
@@ -834,19 +834,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Henry Taylor</v>
+        <v>Owen Young</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E20" s="2" t="str">
         <v/>
       </c>
       <c r="F20" s="2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="21">
@@ -854,19 +854,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Zoe Green</v>
+        <v>Zoe Young</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2" t="str">
         <v/>
       </c>
       <c r="F21" s="2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="22">
@@ -874,19 +874,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Owen King</v>
+        <v>Caleb Anderson</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +894,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Harper Scott</v>
+        <v>Harper Martin</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2" t="str">
         <v/>
       </c>
       <c r="F23" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +914,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Caleb Taylor</v>
+        <v>Ryan Brown</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2" t="str">
         <v/>
       </c>
       <c r="F24" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="25">
@@ -934,19 +934,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Ella Martin</v>
+        <v>Ella Hill</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="str">
         <v/>
       </c>
       <c r="F25" s="2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="26">
@@ -954,19 +954,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Ryan Anderson</v>
+        <v>Isaac Scott</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2" t="str">
         <v/>
       </c>
       <c r="F26" s="2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +974,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Ruby Baker</v>
+        <v>Ruby Nelson</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="2">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F27" s="2" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="28">
@@ -994,19 +994,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Isaac Wilson</v>
+        <v>Samuel White</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2" t="str">
         <v/>
       </c>
       <c r="F28" s="2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="29">
@@ -1014,13 +1014,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Aria Johnson</v>
+        <v>Aria Nelson</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2" t="str">
         <v/>
@@ -1034,19 +1034,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Samuel Smith</v>
+        <v>Daniel King</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="str">
         <v/>
       </c>
       <c r="F30" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="31">
@@ -1054,19 +1054,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Nora Anderson</v>
+        <v>Nora Johnson</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2" t="str">
         <v/>
       </c>
       <c r="F31" s="2" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="32">
@@ -1074,13 +1074,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Daniel Campbell</v>
+        <v>Aiden Johnson</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="2">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2" t="str">
         <v/>
@@ -1094,13 +1094,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Maya Brown</v>
+        <v>Maya Anderson</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D33" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2" t="str">
         <v/>
@@ -1114,7 +1114,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Aiden Young</v>
+        <v>Max Thompson</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="F34" s="2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="35">
@@ -1134,7 +1134,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Leah Nelson</v>
+        <v>Leah Baker</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
@@ -1154,16 +1154,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Max Brown</v>
+        <v>Theo Smith</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F36" s="2" t="str">
         <v>A</v>
@@ -1174,19 +1174,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Ivy Thompson</v>
+        <v>Ivy Adams</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2" t="str">
         <v/>
       </c>
       <c r="F37" s="2" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="38">
@@ -1194,19 +1194,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Theo White</v>
+        <v>Jacob Walker</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D38" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E38" s="2" t="str">
         <v/>
       </c>
       <c r="F38" s="2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="39">
@@ -1214,19 +1214,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Hannah Campbell</v>
+        <v>Hannah Green</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D39" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F39" s="2" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="40">
@@ -1234,19 +1234,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Jacob Scott</v>
+        <v>Eli Johnson</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2" t="str">
         <v/>
       </c>
       <c r="F40" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="41">
@@ -1254,19 +1254,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Amelia Wilson</v>
+        <v>Amelia Anderson</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2" t="str">
         <v/>
       </c>
       <c r="F41" s="2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1274,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Eli Young</v>
+        <v>Liam Brown</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="2">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2" t="str">
         <v/>
       </c>
       <c r="F42" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="43">
@@ -1294,19 +1294,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Emma Brown</v>
+        <v>Olivia Taylor</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2" t="str">
         <v/>
       </c>
       <c r="F43" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="44">
@@ -1314,19 +1314,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Liam Johnson</v>
+        <v>Noah Walker</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="45">
@@ -1334,19 +1334,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Olivia Martin</v>
+        <v>Ava Green</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2" t="str">
         <v/>
       </c>
       <c r="F45" s="2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="46">
@@ -1354,19 +1354,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Noah Walker</v>
+        <v>Oliver Young</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E46" s="2" t="str">
         <v/>
       </c>
       <c r="F46" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="47">
@@ -1374,19 +1374,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Ava Smith</v>
+        <v>Mia Johnson</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D47" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="48">
@@ -1394,13 +1394,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Oliver Adams</v>
+        <v>Ethan Thompson</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D48" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E48" s="2" t="str">
         <v/>
@@ -1414,13 +1414,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Mia Walker</v>
+        <v>Isla Wright</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="2">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E49" s="2" t="str">
         <v/>
@@ -1434,19 +1434,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Ethan Scott</v>
+        <v>Lucas Martin</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="2">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F50" s="2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="51">
@@ -1454,19 +1454,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Grace Scott</v>
+        <v>Grace Johnson</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E51" s="2" t="str">
         <v/>
       </c>
       <c r="F51" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="52">
@@ -1474,13 +1474,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Lucas Adams</v>
+        <v>Mason Scott</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E52" s="2" t="str">
         <v/>
@@ -1494,16 +1494,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Chloe Anderson</v>
+        <v>Chloe Johnson</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="2">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E53" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F53" s="2" t="str">
         <v>B</v>
@@ -1514,19 +1514,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Mason Martin</v>
+        <v>Jack Green</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="2">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E54" s="2" t="str">
         <v/>
       </c>
       <c r="F54" s="2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="55">
@@ -1534,19 +1534,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Lily Hill</v>
+        <v>Lily Wright</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="2">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2" t="str">
         <v/>
       </c>
       <c r="F55" s="2" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="56">
@@ -1554,13 +1554,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Jack Adams</v>
+        <v>Leo Thompson</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E56" s="2" t="str">
         <v/>
@@ -1574,19 +1574,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Zoe King</v>
+        <v>Zoe Taylor</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E57" s="2" t="str">
         <v/>
       </c>
       <c r="F57" s="2" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="58">
@@ -1594,19 +1594,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Leo Brown</v>
+        <v>Henry Martin</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E58" s="2" t="str">
         <v/>
       </c>
       <c r="F58" s="2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="59">
@@ -1614,19 +1614,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Harper Nelson</v>
+        <v>Harper Brown</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D59" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E59" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="F59" s="2" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="60">
@@ -1634,13 +1634,13 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Henry Wilson</v>
+        <v>Owen Anderson</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E60" s="2" t="str">
         <v/>
@@ -1654,13 +1654,13 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Ella Anderson</v>
+        <v>Ella Wright</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D61" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E61" s="2" t="str">
         <v/>
@@ -1674,13 +1674,13 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Owen Anderson</v>
+        <v>Ryan Nelson</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E62" s="2" t="str">
         <v/>
@@ -1694,19 +1694,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Ruby Campbell</v>
+        <v>Ruby Young</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D63" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2" t="str">
         <v/>
       </c>
       <c r="F63" s="2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="64">
@@ -1714,19 +1714,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Caleb Campbell</v>
+        <v>Isaac Hill</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E64" s="2" t="str">
         <v/>
       </c>
       <c r="F64" s="2" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="65">
@@ -1734,19 +1734,19 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Aria Young</v>
+        <v>Aria Wright</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D65" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E65" s="2" t="str">
         <v/>
       </c>
       <c r="F65" s="2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="66">
@@ -1754,13 +1754,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Ryan Walker</v>
+        <v>Samuel Nelson</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E66" s="2" t="str">
         <v/>
@@ -1774,19 +1774,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Nora Taylor</v>
+        <v>Nora Young</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E67" s="2" t="str">
         <v/>
       </c>
       <c r="F67" s="2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="68">
@@ -1794,19 +1794,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Isaac Green</v>
+        <v>Daniel Anderson</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2" t="str">
         <v/>
       </c>
       <c r="F68" s="2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="69">
@@ -1814,19 +1814,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Maya Scott</v>
+        <v>Maya Walker</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E69" s="2" t="str">
         <v/>
       </c>
       <c r="F69" s="2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="70">
@@ -1834,13 +1834,13 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Samuel Nelson</v>
+        <v>Aiden Thompson</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E70" s="2" t="str">
         <v/>
@@ -1854,19 +1854,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Leah Young</v>
+        <v>Leah White</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="2">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E71" s="2" t="str">
         <v/>
       </c>
       <c r="F71" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="72">
@@ -1874,19 +1874,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Daniel Johnson</v>
+        <v>Max Nelson</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E72" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="73">
@@ -1894,19 +1894,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Ivy Hill</v>
+        <v>Ivy White</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E73" s="2" t="str">
         <v/>
       </c>
       <c r="F73" s="2" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="74">
@@ -1914,19 +1914,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Aiden Baker</v>
+        <v>Theo Adams</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E74" s="2" t="str">
         <v/>
       </c>
       <c r="F74" s="2" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="75">
@@ -1934,19 +1934,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Hannah Scott</v>
+        <v>Hannah Martin</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E75" s="2" t="str">
         <v/>
       </c>
       <c r="F75" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="76">
@@ -1954,13 +1954,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Max Campbell</v>
+        <v>Jacob Adams</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E76" s="2" t="str">
         <v/>
@@ -1974,19 +1974,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Amelia Wright</v>
+        <v>Amelia Brown</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2" t="str">
         <v/>
       </c>
       <c r="F77" s="2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="78">
@@ -1994,19 +1994,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Theo Nelson</v>
+        <v>Eli White</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E78" s="2" t="str">
         <v/>
       </c>
       <c r="F78" s="2" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="79">
@@ -2020,13 +2020,13 @@
         <v>F</v>
       </c>
       <c r="D79" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2" t="str">
         <v/>
       </c>
       <c r="F79" s="2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="80">
@@ -2034,19 +2034,19 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Jacob Taylor</v>
+        <v>Liam Scott</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E80" s="2" t="str">
         <v/>
       </c>
       <c r="F80" s="2" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="81">
@@ -2054,13 +2054,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Olivia Taylor</v>
+        <v>Olivia Smith</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="2">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E81" s="2" t="str">
         <v/>
@@ -2074,13 +2074,13 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Eli Taylor</v>
+        <v>Noah Thompson</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E82" s="2" t="str">
         <v/>
@@ -2102,13 +2102,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C1" s="2">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2124,21 +2124,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B1" s="2">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/en/sample2.xlsx
+++ b/public/samples/en/sample2.xlsx
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -468,6 +468,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -483,9 +486,12 @@
         <v>Reading score</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>IEP/504 plan</v>
+        <v>Reading level</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Learning support</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>Previous class</v>
       </c>
     </row>
@@ -494,7 +500,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Emma Green</v>
+        <v>Emma Anderson</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -502,11 +508,14 @@
       <c r="D3" s="2">
         <v>72</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="4">
@@ -514,19 +523,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Liam Wilson</v>
+        <v>Liam White</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="2">
-        <v>79</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +546,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Olivia Anderson</v>
+        <v>Olivia Brown</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="2">
-        <v>84</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>87</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +569,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Noah Hill</v>
+        <v>Noah Walker</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D6" s="2">
-        <v>67</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="7">
@@ -574,18 +592,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Ava Scott</v>
+        <v>Ava Hill</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="2">
-        <v>78</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -594,19 +615,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Oliver Hill</v>
+        <v>Oliver Anderson</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D8" s="2">
-        <v>79</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="9">
@@ -614,19 +638,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Sophia Anderson</v>
+        <v>Sophia Brown</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="2">
-        <v>87</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="10">
@@ -634,18 +661,21 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Ethan Martin</v>
+        <v>Ethan Adams</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="2">
-        <v>75</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>68</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -654,19 +684,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Mia Wright</v>
+        <v>Mia Hill</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="2">
-        <v>69</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
+        <v>84</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="12">
@@ -674,18 +707,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Lucas Brown</v>
+        <v>Lucas Martin</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D12" s="2">
-        <v>77</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -694,18 +730,21 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Isla Martin</v>
+        <v>Isla Thompson</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="2">
-        <v>75</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G13" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -714,19 +753,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Mason Campbell</v>
+        <v>Mason White</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="2">
-        <v>72</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="15">
@@ -734,19 +776,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Grace Thompson</v>
+        <v>Grace Wright</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="2">
-        <v>72</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="16">
@@ -754,19 +799,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Leo Taylor</v>
+        <v>Jack Wilson</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="2">
-        <v>76</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="17">
@@ -774,18 +822,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Chloe Wright</v>
+        <v>Chloe Baker</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="2">
-        <v>83</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
       </c>
       <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -794,18 +845,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Henry Anderson</v>
+        <v>Leo Thompson</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="2">
-        <v>77</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -814,18 +868,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Lily Hill</v>
+        <v>Lily Johnson</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="2">
-        <v>78</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v>✓</v>
+        <v>79</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -834,19 +891,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Owen Young</v>
+        <v>Henry Scott</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="2">
-        <v>86</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="21">
@@ -854,19 +914,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Zoe Young</v>
+        <v>Zoe Brown</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="2">
-        <v>77</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="22">
@@ -874,19 +937,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Caleb Anderson</v>
+        <v>Owen Nelson</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="2">
-        <v>72</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v>✓</v>
+        <v>63</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +960,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Harper Martin</v>
+        <v>Harper Walker</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="2">
-        <v>77</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +983,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Ryan Brown</v>
+        <v>Caleb Wilson</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="2">
-        <v>81</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="25">
@@ -934,19 +1006,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Ella Hill</v>
+        <v>Ella Wilson</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="2">
-        <v>63</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="26">
@@ -954,19 +1029,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Isaac Scott</v>
+        <v>Ryan Smith</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="2">
-        <v>89</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +1052,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Ruby Nelson</v>
+        <v>Ruby Johnson</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="2">
-        <v>69</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="28">
@@ -994,18 +1075,21 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Samuel White</v>
+        <v>Isaac Thompson</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="2">
-        <v>77</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1014,19 +1098,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Aria Nelson</v>
+        <v>Aria Brown</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="2">
-        <v>74</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="30">
@@ -1034,19 +1121,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Daniel King</v>
+        <v>Samuel White</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="2">
-        <v>77</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="31">
@@ -1054,19 +1144,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Nora Johnson</v>
+        <v>Nora Brown</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="2">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>93</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
       </c>
       <c r="F31" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G31" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="32">
@@ -1074,18 +1167,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Aiden Johnson</v>
+        <v>Daniel Thompson</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="2">
-        <v>79</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>67</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1094,19 +1190,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Maya Anderson</v>
+        <v>Maya Walker</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D33" s="2">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5</v>
       </c>
       <c r="F33" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="34">
@@ -1114,18 +1213,21 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Max Thompson</v>
+        <v>Aiden Wright</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="2">
-        <v>71</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1134,19 +1236,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Leah Baker</v>
+        <v>Leah Wright</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="2">
-        <v>80</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E35" s="2">
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="36">
@@ -1154,18 +1259,21 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Theo Smith</v>
+        <v>Max Nelson</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="2">
-        <v>60</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1174,19 +1282,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Ivy Adams</v>
+        <v>Ivy Scott</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="2">
-        <v>74</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E37" s="2">
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="38">
@@ -1194,18 +1305,21 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Jacob Walker</v>
+        <v>Theo Johnson</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D38" s="2">
-        <v>88</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1214,7 +1328,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Hannah Green</v>
+        <v>Hannah Thompson</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
@@ -1222,11 +1336,14 @@
       <c r="D39" s="2">
         <v>77</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+      <c r="E39" s="2">
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="40">
@@ -1234,18 +1351,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Eli Johnson</v>
+        <v>Jacob Young</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="2">
-        <v>84</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E40" s="2">
+        <v>5</v>
       </c>
       <c r="F40" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1254,19 +1374,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Amelia Anderson</v>
+        <v>Amelia Johnson</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="2">
-        <v>86</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1397,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Liam Brown</v>
+        <v>Eli Young</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="2">
-        <v>78</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="43">
@@ -1294,18 +1420,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Olivia Taylor</v>
+        <v>Emma Smith</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="2">
-        <v>82</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
       </c>
       <c r="F43" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1314,19 +1443,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Noah Walker</v>
+        <v>Liam Campbell</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="2">
-        <v>73</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v>✓</v>
+        <v>74</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="45">
@@ -1334,19 +1466,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Ava Green</v>
+        <v>Olivia Campbell</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="2">
-        <v>73</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="46">
@@ -1354,19 +1489,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Oliver Young</v>
+        <v>Noah Anderson</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="2">
-        <v>90</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="47">
@@ -1374,19 +1512,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Mia Johnson</v>
+        <v>Ava Green</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D47" s="2">
-        <v>84</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v>✓</v>
+        <v>63</v>
+      </c>
+      <c r="E47" s="2">
+        <v>3</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="48">
@@ -1394,19 +1535,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Ethan Thompson</v>
+        <v>Oliver Wilson</v>
       </c>
       <c r="C48" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D48" s="2">
-        <v>74</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="49">
@@ -1414,19 +1558,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Isla Wright</v>
+        <v>Sophia Smith</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="2">
-        <v>71</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="50">
@@ -1434,18 +1581,21 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Lucas Martin</v>
+        <v>Ethan Campbell</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="2">
-        <v>62</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1454,19 +1604,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Grace Johnson</v>
+        <v>Mia Green</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="2">
-        <v>88</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>67</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="52">
@@ -1474,19 +1627,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Mason Scott</v>
+        <v>Lucas Wilson</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="2">
-        <v>91</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="53">
@@ -1494,18 +1650,21 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Chloe Johnson</v>
+        <v>Isla Wright</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="2">
-        <v>64</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1514,18 +1673,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Jack Green</v>
+        <v>Mason Nelson</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="2">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E54" s="2">
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1534,19 +1696,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Lily Wright</v>
+        <v>Grace Taylor</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="2">
-        <v>82</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E55" s="2">
+        <v>5</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="56">
@@ -1554,19 +1719,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Leo Thompson</v>
+        <v>Jack Hill</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="2">
-        <v>63</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="E56" s="2">
+        <v>5</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="57">
@@ -1574,19 +1742,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Zoe Taylor</v>
+        <v>Chloe Green</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="2">
-        <v>67</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="58">
@@ -1594,19 +1765,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Henry Martin</v>
+        <v>Leo Taylor</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="2">
-        <v>88</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="59">
@@ -1614,19 +1788,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Harper Brown</v>
+        <v>Lily White</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D59" s="2">
-        <v>69</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E59" s="2">
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="60">
@@ -1634,19 +1811,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Owen Anderson</v>
+        <v>Henry Walker</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E60" s="2">
+        <v>4</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="61">
@@ -1654,7 +1834,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Ella Wright</v>
+        <v>Zoe Wilson</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
@@ -1662,10 +1842,13 @@
       <c r="D61" s="2">
         <v>76</v>
       </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+      <c r="E61" s="2">
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1674,19 +1857,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Ryan Nelson</v>
+        <v>Owen Taylor</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="2">
-        <v>77</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="63">
@@ -1694,19 +1880,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Ruby Young</v>
+        <v>Harper Wilson</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D63" s="2">
-        <v>83</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>64</v>
+      </c>
+      <c r="E63" s="2">
+        <v>4</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="64">
@@ -1714,18 +1903,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Isaac Hill</v>
+        <v>Caleb Baker</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="2">
-        <v>68</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1734,19 +1926,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Aria Wright</v>
+        <v>Ella Scott</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D65" s="2">
-        <v>87</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E65" s="2">
+        <v>4</v>
       </c>
       <c r="F65" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="66">
@@ -1754,19 +1949,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Samuel Nelson</v>
+        <v>Ryan Adams</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="2">
-        <v>84</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E66" s="2">
+        <v>5</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="67">
@@ -1774,18 +1972,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Nora Young</v>
+        <v>Ruby Nelson</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="2">
-        <v>76</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G67" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1794,19 +1995,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Daniel Anderson</v>
+        <v>Isaac King</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="2">
-        <v>85</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>90</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="69">
@@ -1814,19 +2018,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Maya Walker</v>
+        <v>Aria King</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="2">
-        <v>80</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="70">
@@ -1834,19 +2041,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Aiden Thompson</v>
+        <v>Samuel Taylor</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="2">
-        <v>76</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="71">
@@ -1854,19 +2064,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Leah White</v>
+        <v>Nora Scott</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="2">
-        <v>78</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>3</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="72">
@@ -1874,19 +2087,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Max Nelson</v>
+        <v>Daniel Brown</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="2">
-        <v>67</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v>✓</v>
+        <v>70</v>
+      </c>
+      <c r="E72" s="2">
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="73">
@@ -1894,19 +2110,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Ivy White</v>
+        <v>Maya Wright</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="2">
-        <v>80</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>62</v>
+      </c>
+      <c r="E73" s="2">
+        <v>5</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="74">
@@ -1914,19 +2133,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Theo Adams</v>
+        <v>Aiden Campbell</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="2">
-        <v>78</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E74" s="2">
+        <v>1</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="75">
@@ -1934,19 +2156,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Hannah Martin</v>
+        <v>Leah Adams</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="2">
-        <v>88</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E75" s="2">
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G75" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="76">
@@ -1954,18 +2179,21 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Jacob Adams</v>
+        <v>Max Anderson</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="2">
-        <v>80</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E76" s="2">
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1974,19 +2202,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Amelia Brown</v>
+        <v>Ivy Young</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="2">
-        <v>82</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="78">
@@ -1994,18 +2225,21 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Eli White</v>
+        <v>Theo Wilson</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="2">
-        <v>90</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -2014,19 +2248,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Emma Nelson</v>
+        <v>Hannah Campbell</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="2">
-        <v>78</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="80">
@@ -2034,19 +2271,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Liam Scott</v>
+        <v>Jacob Smith</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="2">
-        <v>70</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E80" s="2">
+        <v>5</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="81">
@@ -2054,19 +2294,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Olivia Smith</v>
+        <v>Amelia Young</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="2">
-        <v>66</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E81" s="2">
+        <v>4</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="82">
@@ -2074,24 +2317,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Noah Thompson</v>
+        <v>Eli Johnson</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="2">
-        <v>77</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2102,13 +2348,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C1" s="2">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2124,21 +2370,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/en/sample2.xlsx
+++ b/public/samples/en/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Roster" sheetId="2" r:id="rId2"/>
     <sheet name="Keep together" sheetId="3" r:id="rId3"/>
     <sheet name="Keep apart" sheetId="4" r:id="rId4"/>
+    <sheet name="Attributes" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -618,7 +619,7 @@
         <v>Oliver Anderson</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D8" s="2">
         <v>86</v>
@@ -963,7 +964,7 @@
         <v>Harper Walker</v>
       </c>
       <c r="C23" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D23" s="2">
         <v>78</v>
@@ -1538,7 +1539,7 @@
         <v>Oliver Wilson</v>
       </c>
       <c r="C48" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D48" s="2">
         <v>82</v>
@@ -1883,7 +1884,7 @@
         <v>Harper Wilson</v>
       </c>
       <c r="C63" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D63" s="2">
         <v>64</v>
@@ -2392,4 +2393,87 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Attribute</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Options</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Reading score</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Number</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Reading level</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Scale</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Learning support</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Previous class</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/en/sample2.xlsx
+++ b/public/samples/en/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Roster" sheetId="2" r:id="rId2"/>
     <sheet name="Keep together" sheetId="3" r:id="rId3"/>
     <sheet name="Keep apart" sheetId="4" r:id="rId4"/>
+    <sheet name="Attributes" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -447,7 +448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -468,6 +469,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -483,9 +487,12 @@
         <v>Reading score</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>IEP/504 plan</v>
+        <v>Reading level</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Learning support</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>Previous class</v>
       </c>
     </row>
@@ -494,7 +501,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Emma Green</v>
+        <v>Emma Anderson</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -502,11 +509,14 @@
       <c r="D3" s="2">
         <v>72</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="4">
@@ -514,19 +524,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Liam Wilson</v>
+        <v>Liam White</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="2">
-        <v>79</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +547,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Olivia Anderson</v>
+        <v>Olivia Brown</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="2">
-        <v>84</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>87</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +570,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Noah Hill</v>
+        <v>Noah Walker</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D6" s="2">
-        <v>67</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="7">
@@ -574,18 +593,21 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Ava Scott</v>
+        <v>Ava Hill</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="2">
-        <v>78</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -594,19 +616,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Oliver Hill</v>
+        <v>Oliver Anderson</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D8" s="2">
-        <v>79</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="9">
@@ -614,19 +639,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Sophia Anderson</v>
+        <v>Sophia Brown</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="2">
-        <v>87</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="10">
@@ -634,18 +662,21 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Ethan Martin</v>
+        <v>Ethan Adams</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="2">
-        <v>75</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>68</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -654,19 +685,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Mia Wright</v>
+        <v>Mia Hill</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="2">
-        <v>69</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
+        <v>84</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="12">
@@ -674,18 +708,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Lucas Brown</v>
+        <v>Lucas Martin</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D12" s="2">
-        <v>77</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -694,18 +731,21 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Isla Martin</v>
+        <v>Isla Thompson</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="2">
-        <v>75</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G13" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -714,19 +754,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Mason Campbell</v>
+        <v>Mason White</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="2">
-        <v>72</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="15">
@@ -734,19 +777,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Grace Thompson</v>
+        <v>Grace Wright</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="2">
-        <v>72</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="16">
@@ -754,19 +800,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Leo Taylor</v>
+        <v>Jack Wilson</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="2">
-        <v>76</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="17">
@@ -774,18 +823,21 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Chloe Wright</v>
+        <v>Chloe Baker</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="2">
-        <v>83</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
       </c>
       <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -794,18 +846,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Henry Anderson</v>
+        <v>Leo Thompson</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="2">
-        <v>77</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -814,18 +869,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Lily Hill</v>
+        <v>Lily Johnson</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="2">
-        <v>78</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v>✓</v>
+        <v>79</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -834,19 +892,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Owen Young</v>
+        <v>Henry Scott</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="2">
-        <v>86</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="21">
@@ -854,19 +915,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Zoe Young</v>
+        <v>Zoe Brown</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="2">
-        <v>77</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="22">
@@ -874,19 +938,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Caleb Anderson</v>
+        <v>Owen Nelson</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="2">
-        <v>72</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v>✓</v>
+        <v>63</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +961,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Harper Martin</v>
+        <v>Harper Walker</v>
       </c>
       <c r="C23" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D23" s="2">
-        <v>77</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +984,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Ryan Brown</v>
+        <v>Caleb Wilson</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="2">
-        <v>81</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="25">
@@ -934,19 +1007,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Ella Hill</v>
+        <v>Ella Wilson</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="2">
-        <v>63</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="26">
@@ -954,19 +1030,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Isaac Scott</v>
+        <v>Ryan Smith</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="2">
-        <v>89</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +1053,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Ruby Nelson</v>
+        <v>Ruby Johnson</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="2">
-        <v>69</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="28">
@@ -994,18 +1076,21 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Samuel White</v>
+        <v>Isaac Thompson</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="2">
-        <v>77</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1014,19 +1099,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Aria Nelson</v>
+        <v>Aria Brown</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="2">
-        <v>74</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="30">
@@ -1034,19 +1122,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Daniel King</v>
+        <v>Samuel White</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="2">
-        <v>77</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="31">
@@ -1054,19 +1145,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Nora Johnson</v>
+        <v>Nora Brown</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="2">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>93</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
       </c>
       <c r="F31" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G31" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="32">
@@ -1074,18 +1168,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Aiden Johnson</v>
+        <v>Daniel Thompson</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="2">
-        <v>79</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>67</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1094,19 +1191,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Maya Anderson</v>
+        <v>Maya Walker</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D33" s="2">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5</v>
       </c>
       <c r="F33" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="34">
@@ -1114,18 +1214,21 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Max Thompson</v>
+        <v>Aiden Wright</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="2">
-        <v>71</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1134,19 +1237,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Leah Baker</v>
+        <v>Leah Wright</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="2">
-        <v>80</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E35" s="2">
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="36">
@@ -1154,18 +1260,21 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Theo Smith</v>
+        <v>Max Nelson</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="2">
-        <v>60</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1174,19 +1283,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Ivy Adams</v>
+        <v>Ivy Scott</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="2">
-        <v>74</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E37" s="2">
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="38">
@@ -1194,18 +1306,21 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Jacob Walker</v>
+        <v>Theo Johnson</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D38" s="2">
-        <v>88</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1214,7 +1329,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Hannah Green</v>
+        <v>Hannah Thompson</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
@@ -1222,11 +1337,14 @@
       <c r="D39" s="2">
         <v>77</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+      <c r="E39" s="2">
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="40">
@@ -1234,18 +1352,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Eli Johnson</v>
+        <v>Jacob Young</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="2">
-        <v>84</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E40" s="2">
+        <v>5</v>
       </c>
       <c r="F40" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1254,19 +1375,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Amelia Anderson</v>
+        <v>Amelia Johnson</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="2">
-        <v>86</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1398,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Liam Brown</v>
+        <v>Eli Young</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="2">
-        <v>78</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="43">
@@ -1294,18 +1421,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Olivia Taylor</v>
+        <v>Emma Smith</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="2">
-        <v>82</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
       </c>
       <c r="F43" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1314,19 +1444,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Noah Walker</v>
+        <v>Liam Campbell</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="2">
-        <v>73</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v>✓</v>
+        <v>74</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="45">
@@ -1334,19 +1467,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Ava Green</v>
+        <v>Olivia Campbell</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="2">
-        <v>73</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="46">
@@ -1354,19 +1490,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Oliver Young</v>
+        <v>Noah Anderson</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="2">
-        <v>90</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="47">
@@ -1374,19 +1513,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Mia Johnson</v>
+        <v>Ava Green</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D47" s="2">
-        <v>84</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v>✓</v>
+        <v>63</v>
+      </c>
+      <c r="E47" s="2">
+        <v>3</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="48">
@@ -1394,19 +1536,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Ethan Thompson</v>
+        <v>Oliver Wilson</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D48" s="2">
-        <v>74</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="49">
@@ -1414,19 +1559,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Isla Wright</v>
+        <v>Sophia Smith</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="2">
-        <v>71</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="50">
@@ -1434,18 +1582,21 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Lucas Martin</v>
+        <v>Ethan Campbell</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="2">
-        <v>62</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1454,19 +1605,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Grace Johnson</v>
+        <v>Mia Green</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="2">
-        <v>88</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>67</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="52">
@@ -1474,19 +1628,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Mason Scott</v>
+        <v>Lucas Wilson</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="2">
-        <v>91</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="53">
@@ -1494,18 +1651,21 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Chloe Johnson</v>
+        <v>Isla Wright</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="2">
-        <v>64</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1514,18 +1674,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Jack Green</v>
+        <v>Mason Nelson</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="2">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E54" s="2">
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1534,19 +1697,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Lily Wright</v>
+        <v>Grace Taylor</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="2">
-        <v>82</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E55" s="2">
+        <v>5</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="56">
@@ -1554,19 +1720,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Leo Thompson</v>
+        <v>Jack Hill</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="2">
-        <v>63</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="E56" s="2">
+        <v>5</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="57">
@@ -1574,19 +1743,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Zoe Taylor</v>
+        <v>Chloe Green</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="2">
-        <v>67</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="58">
@@ -1594,19 +1766,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Henry Martin</v>
+        <v>Leo Taylor</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="2">
-        <v>88</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="59">
@@ -1614,19 +1789,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Harper Brown</v>
+        <v>Lily White</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D59" s="2">
-        <v>69</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E59" s="2">
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="60">
@@ -1634,19 +1812,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Owen Anderson</v>
+        <v>Henry Walker</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E60" s="2">
+        <v>4</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="61">
@@ -1654,7 +1835,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Ella Wright</v>
+        <v>Zoe Wilson</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
@@ -1662,10 +1843,13 @@
       <c r="D61" s="2">
         <v>76</v>
       </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+      <c r="E61" s="2">
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1674,19 +1858,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Ryan Nelson</v>
+        <v>Owen Taylor</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="2">
-        <v>77</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="63">
@@ -1694,19 +1881,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Ruby Young</v>
+        <v>Harper Wilson</v>
       </c>
       <c r="C63" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D63" s="2">
-        <v>83</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>64</v>
+      </c>
+      <c r="E63" s="2">
+        <v>4</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="64">
@@ -1714,18 +1904,21 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Isaac Hill</v>
+        <v>Caleb Baker</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="2">
-        <v>68</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1734,19 +1927,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Aria Wright</v>
+        <v>Ella Scott</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D65" s="2">
-        <v>87</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E65" s="2">
+        <v>4</v>
       </c>
       <c r="F65" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="66">
@@ -1754,19 +1950,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Samuel Nelson</v>
+        <v>Ryan Adams</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="2">
-        <v>84</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E66" s="2">
+        <v>5</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="67">
@@ -1774,18 +1973,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Nora Young</v>
+        <v>Ruby Nelson</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="2">
-        <v>76</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G67" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1794,19 +1996,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Daniel Anderson</v>
+        <v>Isaac King</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="2">
-        <v>85</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>90</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="69">
@@ -1814,19 +2019,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Maya Walker</v>
+        <v>Aria King</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="2">
-        <v>80</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="70">
@@ -1834,19 +2042,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Aiden Thompson</v>
+        <v>Samuel Taylor</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="2">
-        <v>76</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>82</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="71">
@@ -1854,19 +2065,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Leah White</v>
+        <v>Nora Scott</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="2">
-        <v>78</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>3</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="72">
@@ -1874,19 +2088,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Max Nelson</v>
+        <v>Daniel Brown</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="2">
-        <v>67</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v>✓</v>
+        <v>70</v>
+      </c>
+      <c r="E72" s="2">
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="73">
@@ -1894,19 +2111,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Ivy White</v>
+        <v>Maya Wright</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="2">
-        <v>80</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>62</v>
+      </c>
+      <c r="E73" s="2">
+        <v>5</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="74">
@@ -1914,19 +2134,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Theo Adams</v>
+        <v>Aiden Campbell</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="2">
-        <v>78</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E74" s="2">
+        <v>1</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="75">
@@ -1934,19 +2157,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Hannah Martin</v>
+        <v>Leah Adams</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="2">
-        <v>88</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E75" s="2">
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G75" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="76">
@@ -1954,18 +2180,21 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Jacob Adams</v>
+        <v>Max Anderson</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="2">
-        <v>80</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E76" s="2">
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1974,19 +2203,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Amelia Brown</v>
+        <v>Ivy Young</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="2">
-        <v>82</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="78">
@@ -1994,18 +2226,21 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Eli White</v>
+        <v>Theo Wilson</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="2">
-        <v>90</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -2014,19 +2249,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Emma Nelson</v>
+        <v>Hannah Campbell</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="2">
-        <v>78</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="80">
@@ -2034,19 +2272,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Liam Scott</v>
+        <v>Jacob Smith</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="2">
-        <v>70</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E80" s="2">
+        <v>5</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="81">
@@ -2054,19 +2295,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Olivia Smith</v>
+        <v>Amelia Young</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="2">
-        <v>66</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E81" s="2">
+        <v>4</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="82">
@@ -2074,24 +2318,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Noah Thompson</v>
+        <v>Eli Johnson</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="2">
-        <v>77</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2102,13 +2349,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C1" s="2">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2124,21 +2371,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2146,4 +2393,87 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Attribute</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Options</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Reading score</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Number</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Reading level</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Scale</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Learning support</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Previous class</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>